--- a/Result/profitability/6725.xlsx
+++ b/Result/profitability/6725.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM24"/>
+  <dimension ref="A1:AM25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3478,6 +3478,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>6725</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>946</v>
+      </c>
+      <c r="D25" t="n">
+        <v>733</v>
+      </c>
+      <c r="E25" t="n">
+        <v>212</v>
+      </c>
+      <c r="F25" t="n">
+        <v>22.46</v>
+      </c>
+      <c r="G25" t="n">
+        <v>97</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>10.22%</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>97</v>
+      </c>
+      <c r="K25" t="n">
+        <v>84</v>
+      </c>
+      <c r="L25" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.6725</v>
+      </c>
+      <c r="N25" t="n">
+        <v>25.70875</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
+      </c>
+      <c r="V25" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-0.3300000000000001</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-0.1274131274131275</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>-0.8499999999999979</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-0.0364650364650364</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.036036036036036</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.600000000000001</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.1309164149043305</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK25" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
